--- a/guides/tutoring_calendar.xlsx
+++ b/guides/tutoring_calendar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cappe/Desktop/BWTHW/bwthw/guides/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539C1476-1D8C-8F41-B99E-C8E63B3C772C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F351E82B-97DC-4544-A48B-77EACEB70066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4000" yWindow="4220" windowWidth="28800" windowHeight="15980" xr2:uid="{53EB7497-E9FB-664A-B8A3-B594D54FB545}"/>
+    <workbookView xWindow="11100" yWindow="1600" windowWidth="28800" windowHeight="15980" xr2:uid="{53EB7497-E9FB-664A-B8A3-B594D54FB545}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>Day</t>
   </si>
@@ -71,22 +71,28 @@
     <t>Tutoring 8: Algorithm</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>14:30 - 16:30</t>
   </si>
   <si>
-    <t>08:30 - 10:30</t>
-  </si>
-  <si>
-    <t>Te+Ue</t>
+    <t>8:30 - 10:30</t>
+  </si>
+  <si>
+    <t>Me</t>
+  </si>
+  <si>
+    <t>DEI/D</t>
+  </si>
+  <si>
+    <t>Te</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -182,13 +188,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -198,21 +204,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,44 +616,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>45726</v>
+      <c r="A5" s="6">
+        <v>45723</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -654,13 +661,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
-        <v>45733</v>
+        <v>45730</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>5</v>
@@ -668,13 +675,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
-        <v>45747</v>
+        <v>45744</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>13</v>
@@ -682,13 +689,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
-        <v>45761</v>
+        <v>45758</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>6</v>
@@ -699,10 +706,10 @@
         <v>45775</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>7</v>
@@ -710,13 +717,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
-        <v>45789</v>
+        <v>45786</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
@@ -724,13 +731,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
-        <v>45796</v>
+        <v>45793</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -738,13 +745,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
-        <v>45803</v>
-      </c>
-      <c r="B12" s="2" t="s">
+        <v>45800</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>15</v>
+      <c r="C12" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -754,11 +761,11 @@
       <c r="A13" s="6">
         <v>45812</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
+      <c r="B13" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
